--- a/template/template.xlsx
+++ b/template/template.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\desktop-fbvhaoa\Share\work\0310_AI\007_webapl\project\excel-input-sample-app-poc\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\0310_AI\007_webapl\apl\excel-input-sample-app-poc\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3512D707-C647-450A-9C5F-89F4F3A86CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C38B217-E441-4092-A5C3-E7E5AE6081BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23175" yWindow="2790" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="1" sheetId="1" r:id="rId1"/>
-    <sheet name="2" sheetId="2" r:id="rId2"/>
+    <sheet name="Print" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -121,12 +121,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -454,31 +453,31 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="str">
-        <f>IF('2'!A2&gt;0,'2'!A2,"")</f>
-        <v/>
-      </c>
-      <c r="D4" s="4" t="str">
-        <f>IF('2'!B2&lt;&gt;"",'2'!B2,"")</f>
-        <v/>
-      </c>
-      <c r="E4" s="4" t="str">
-        <f>IF('2'!C2&lt;&gt;"",'2'!C2,"")</f>
-        <v/>
-      </c>
-      <c r="F4" s="4" t="str">
-        <f>IF('2'!D2&lt;&gt;"",'2'!D2,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="4" t="str">
-        <f>IF('2'!E2&lt;&gt;"",'2'!E2,"")</f>
-        <v/>
-      </c>
-      <c r="H4" s="4" t="str">
-        <f>IF('2'!F2&lt;&gt;"",'2'!F2,"")</f>
-        <v/>
-      </c>
-      <c r="I4" s="4" t="str">
-        <f>IF('2'!G2&lt;&gt;"",'2'!G2,"")</f>
+        <f>IF(Data!A2&gt;0,Data!A2,"")</f>
+        <v/>
+      </c>
+      <c r="D4" s="1" t="str">
+        <f>IF(Data!B2&lt;&gt;"",Data!B2,"")</f>
+        <v/>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f>IF(Data!C2&lt;&gt;"",Data!C2,"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="1" t="str">
+        <f>IF(Data!D2&lt;&gt;"",Data!D2,"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="1" t="str">
+        <f>IF(Data!E2&lt;&gt;"",Data!E2,"")</f>
+        <v/>
+      </c>
+      <c r="H4" s="1" t="str">
+        <f>IF(Data!F2&lt;&gt;"",Data!F2,"")</f>
+        <v/>
+      </c>
+      <c r="I4" s="1" t="str">
+        <f>IF(Data!G2&lt;&gt;"",Data!G2,"")</f>
         <v/>
       </c>
     </row>
@@ -487,31 +486,31 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="str">
-        <f>IF('2'!A3&gt;0,'2'!A3,"")</f>
-        <v/>
-      </c>
-      <c r="D5" s="4" t="str">
-        <f>IF('2'!B3&lt;&gt;"",'2'!B3,"")</f>
-        <v/>
-      </c>
-      <c r="E5" s="4" t="str">
-        <f>IF('2'!C3&lt;&gt;"",'2'!C3,"")</f>
-        <v/>
-      </c>
-      <c r="F5" s="4" t="str">
-        <f>IF('2'!D3&lt;&gt;"",'2'!D3,"")</f>
-        <v/>
-      </c>
-      <c r="G5" s="4" t="str">
-        <f>IF('2'!E3&lt;&gt;"",'2'!E3,"")</f>
-        <v/>
-      </c>
-      <c r="H5" s="4" t="str">
-        <f>IF('2'!F3&lt;&gt;"",'2'!F3,"")</f>
-        <v/>
-      </c>
-      <c r="I5" s="4" t="str">
-        <f>IF('2'!G3&lt;&gt;"",'2'!G3,"")</f>
+        <f>IF(Data!A3&gt;0,Data!A3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="1" t="str">
+        <f>IF(Data!B3&lt;&gt;"",Data!B3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>IF(Data!C3&lt;&gt;"",Data!C3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="1" t="str">
+        <f>IF(Data!D3&lt;&gt;"",Data!D3,"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="1" t="str">
+        <f>IF(Data!E3&lt;&gt;"",Data!E3,"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="1" t="str">
+        <f>IF(Data!F3&lt;&gt;"",Data!F3,"")</f>
+        <v/>
+      </c>
+      <c r="I5" s="1" t="str">
+        <f>IF(Data!G3&lt;&gt;"",Data!G3,"")</f>
         <v/>
       </c>
     </row>
@@ -520,31 +519,31 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="str">
-        <f>IF('2'!A4&gt;0,'2'!A4,"")</f>
-        <v/>
-      </c>
-      <c r="D6" s="4" t="str">
-        <f>IF('2'!B4&lt;&gt;"",'2'!B4,"")</f>
-        <v/>
-      </c>
-      <c r="E6" s="4" t="str">
-        <f>IF('2'!C4&lt;&gt;"",'2'!C4,"")</f>
-        <v/>
-      </c>
-      <c r="F6" s="4" t="str">
-        <f>IF('2'!D4&lt;&gt;"",'2'!D4,"")</f>
-        <v/>
-      </c>
-      <c r="G6" s="4" t="str">
-        <f>IF('2'!E4&lt;&gt;"",'2'!E4,"")</f>
-        <v/>
-      </c>
-      <c r="H6" s="4" t="str">
-        <f>IF('2'!F4&lt;&gt;"",'2'!F4,"")</f>
-        <v/>
-      </c>
-      <c r="I6" s="4" t="str">
-        <f>IF('2'!G4&lt;&gt;"",'2'!G4,"")</f>
+        <f>IF(Data!A4&gt;0,Data!A4,"")</f>
+        <v/>
+      </c>
+      <c r="D6" s="1" t="str">
+        <f>IF(Data!B4&lt;&gt;"",Data!B4,"")</f>
+        <v/>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f>IF(Data!C4&lt;&gt;"",Data!C4,"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="1" t="str">
+        <f>IF(Data!D4&lt;&gt;"",Data!D4,"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="1" t="str">
+        <f>IF(Data!E4&lt;&gt;"",Data!E4,"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="1" t="str">
+        <f>IF(Data!F4&lt;&gt;"",Data!F4,"")</f>
+        <v/>
+      </c>
+      <c r="I6" s="1" t="str">
+        <f>IF(Data!G4&lt;&gt;"",Data!G4,"")</f>
         <v/>
       </c>
     </row>
@@ -553,31 +552,31 @@
         <v>4</v>
       </c>
       <c r="C7" s="2" t="str">
-        <f>IF('2'!A5&gt;0,'2'!A5,"")</f>
-        <v/>
-      </c>
-      <c r="D7" s="4" t="str">
-        <f>IF('2'!B5&lt;&gt;"",'2'!B5,"")</f>
-        <v/>
-      </c>
-      <c r="E7" s="4" t="str">
-        <f>IF('2'!C5&lt;&gt;"",'2'!C5,"")</f>
-        <v/>
-      </c>
-      <c r="F7" s="4" t="str">
-        <f>IF('2'!D5&lt;&gt;"",'2'!D5,"")</f>
-        <v/>
-      </c>
-      <c r="G7" s="4" t="str">
-        <f>IF('2'!E5&lt;&gt;"",'2'!E5,"")</f>
-        <v/>
-      </c>
-      <c r="H7" s="4" t="str">
-        <f>IF('2'!F5&lt;&gt;"",'2'!F5,"")</f>
-        <v/>
-      </c>
-      <c r="I7" s="4" t="str">
-        <f>IF('2'!G5&lt;&gt;"",'2'!G5,"")</f>
+        <f>IF(Data!A5&gt;0,Data!A5,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="1" t="str">
+        <f>IF(Data!B5&lt;&gt;"",Data!B5,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f>IF(Data!C5&lt;&gt;"",Data!C5,"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="1" t="str">
+        <f>IF(Data!D5&lt;&gt;"",Data!D5,"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="1" t="str">
+        <f>IF(Data!E5&lt;&gt;"",Data!E5,"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="1" t="str">
+        <f>IF(Data!F5&lt;&gt;"",Data!F5,"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="1" t="str">
+        <f>IF(Data!G5&lt;&gt;"",Data!G5,"")</f>
         <v/>
       </c>
     </row>
@@ -586,31 +585,31 @@
         <v>5</v>
       </c>
       <c r="C8" s="2" t="str">
-        <f>IF('2'!A6&gt;0,'2'!A6,"")</f>
-        <v/>
-      </c>
-      <c r="D8" s="4" t="str">
-        <f>IF('2'!B6&lt;&gt;"",'2'!B6,"")</f>
-        <v/>
-      </c>
-      <c r="E8" s="4" t="str">
-        <f>IF('2'!C6&lt;&gt;"",'2'!C6,"")</f>
-        <v/>
-      </c>
-      <c r="F8" s="4" t="str">
-        <f>IF('2'!D6&lt;&gt;"",'2'!D6,"")</f>
-        <v/>
-      </c>
-      <c r="G8" s="4" t="str">
-        <f>IF('2'!E6&lt;&gt;"",'2'!E6,"")</f>
-        <v/>
-      </c>
-      <c r="H8" s="4" t="str">
-        <f>IF('2'!F6&lt;&gt;"",'2'!F6,"")</f>
-        <v/>
-      </c>
-      <c r="I8" s="4" t="str">
-        <f>IF('2'!G6&lt;&gt;"",'2'!G6,"")</f>
+        <f>IF(Data!A6&gt;0,Data!A6,"")</f>
+        <v/>
+      </c>
+      <c r="D8" s="1" t="str">
+        <f>IF(Data!B6&lt;&gt;"",Data!B6,"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f>IF(Data!C6&lt;&gt;"",Data!C6,"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="1" t="str">
+        <f>IF(Data!D6&lt;&gt;"",Data!D6,"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="1" t="str">
+        <f>IF(Data!E6&lt;&gt;"",Data!E6,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="1" t="str">
+        <f>IF(Data!F6&lt;&gt;"",Data!F6,"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="1" t="str">
+        <f>IF(Data!G6&lt;&gt;"",Data!G6,"")</f>
         <v/>
       </c>
     </row>
@@ -619,31 +618,31 @@
         <v>6</v>
       </c>
       <c r="C9" s="2" t="str">
-        <f>IF('2'!A7&gt;0,'2'!A7,"")</f>
-        <v/>
-      </c>
-      <c r="D9" s="4" t="str">
-        <f>IF('2'!B7&lt;&gt;"",'2'!B7,"")</f>
-        <v/>
-      </c>
-      <c r="E9" s="4" t="str">
-        <f>IF('2'!C7&lt;&gt;"",'2'!C7,"")</f>
-        <v/>
-      </c>
-      <c r="F9" s="4" t="str">
-        <f>IF('2'!D7&lt;&gt;"",'2'!D7,"")</f>
-        <v/>
-      </c>
-      <c r="G9" s="4" t="str">
-        <f>IF('2'!E7&lt;&gt;"",'2'!E7,"")</f>
-        <v/>
-      </c>
-      <c r="H9" s="4" t="str">
-        <f>IF('2'!F7&lt;&gt;"",'2'!F7,"")</f>
-        <v/>
-      </c>
-      <c r="I9" s="4" t="str">
-        <f>IF('2'!G7&lt;&gt;"",'2'!G7,"")</f>
+        <f>IF(Data!A7&gt;0,Data!A7,"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="1" t="str">
+        <f>IF(Data!B7&lt;&gt;"",Data!B7,"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f>IF(Data!C7&lt;&gt;"",Data!C7,"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="1" t="str">
+        <f>IF(Data!D7&lt;&gt;"",Data!D7,"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="1" t="str">
+        <f>IF(Data!E7&lt;&gt;"",Data!E7,"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="1" t="str">
+        <f>IF(Data!F7&lt;&gt;"",Data!F7,"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="1" t="str">
+        <f>IF(Data!G7&lt;&gt;"",Data!G7,"")</f>
         <v/>
       </c>
     </row>
@@ -652,31 +651,31 @@
         <v>7</v>
       </c>
       <c r="C10" s="2" t="str">
-        <f>IF('2'!A8&gt;0,'2'!A8,"")</f>
-        <v/>
-      </c>
-      <c r="D10" s="4" t="str">
-        <f>IF('2'!B8&lt;&gt;"",'2'!B8,"")</f>
-        <v/>
-      </c>
-      <c r="E10" s="4" t="str">
-        <f>IF('2'!C8&lt;&gt;"",'2'!C8,"")</f>
-        <v/>
-      </c>
-      <c r="F10" s="4" t="str">
-        <f>IF('2'!D8&lt;&gt;"",'2'!D8,"")</f>
-        <v/>
-      </c>
-      <c r="G10" s="4" t="str">
-        <f>IF('2'!E8&lt;&gt;"",'2'!E8,"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="4" t="str">
-        <f>IF('2'!F8&lt;&gt;"",'2'!F8,"")</f>
-        <v/>
-      </c>
-      <c r="I10" s="4" t="str">
-        <f>IF('2'!G8&lt;&gt;"",'2'!G8,"")</f>
+        <f>IF(Data!A8&gt;0,Data!A8,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="1" t="str">
+        <f>IF(Data!B8&lt;&gt;"",Data!B8,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f>IF(Data!C8&lt;&gt;"",Data!C8,"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="1" t="str">
+        <f>IF(Data!D8&lt;&gt;"",Data!D8,"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="1" t="str">
+        <f>IF(Data!E8&lt;&gt;"",Data!E8,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="1" t="str">
+        <f>IF(Data!F8&lt;&gt;"",Data!F8,"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="1" t="str">
+        <f>IF(Data!G8&lt;&gt;"",Data!G8,"")</f>
         <v/>
       </c>
     </row>
@@ -685,31 +684,31 @@
         <v>8</v>
       </c>
       <c r="C11" s="2" t="str">
-        <f>IF('2'!A9&gt;0,'2'!A9,"")</f>
-        <v/>
-      </c>
-      <c r="D11" s="4" t="str">
-        <f>IF('2'!B9&lt;&gt;"",'2'!B9,"")</f>
-        <v/>
-      </c>
-      <c r="E11" s="4" t="str">
-        <f>IF('2'!C9&lt;&gt;"",'2'!C9,"")</f>
-        <v/>
-      </c>
-      <c r="F11" s="4" t="str">
-        <f>IF('2'!D9&lt;&gt;"",'2'!D9,"")</f>
-        <v/>
-      </c>
-      <c r="G11" s="4" t="str">
-        <f>IF('2'!E9&lt;&gt;"",'2'!E9,"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="4" t="str">
-        <f>IF('2'!F9&lt;&gt;"",'2'!F9,"")</f>
-        <v/>
-      </c>
-      <c r="I11" s="4" t="str">
-        <f>IF('2'!G9&lt;&gt;"",'2'!G9,"")</f>
+        <f>IF(Data!A9&gt;0,Data!A9,"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="1" t="str">
+        <f>IF(Data!B9&lt;&gt;"",Data!B9,"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f>IF(Data!C9&lt;&gt;"",Data!C9,"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="1" t="str">
+        <f>IF(Data!D9&lt;&gt;"",Data!D9,"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="1" t="str">
+        <f>IF(Data!E9&lt;&gt;"",Data!E9,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="1" t="str">
+        <f>IF(Data!F9&lt;&gt;"",Data!F9,"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="1" t="str">
+        <f>IF(Data!G9&lt;&gt;"",Data!G9,"")</f>
         <v/>
       </c>
     </row>
@@ -718,31 +717,31 @@
         <v>9</v>
       </c>
       <c r="C12" s="2" t="str">
-        <f>IF('2'!A10&gt;0,'2'!A10,"")</f>
-        <v/>
-      </c>
-      <c r="D12" s="4" t="str">
-        <f>IF('2'!B10&lt;&gt;"",'2'!B10,"")</f>
-        <v/>
-      </c>
-      <c r="E12" s="4" t="str">
-        <f>IF('2'!C10&lt;&gt;"",'2'!C10,"")</f>
-        <v/>
-      </c>
-      <c r="F12" s="4" t="str">
-        <f>IF('2'!D10&lt;&gt;"",'2'!D10,"")</f>
-        <v/>
-      </c>
-      <c r="G12" s="4" t="str">
-        <f>IF('2'!E10&lt;&gt;"",'2'!E10,"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="4" t="str">
-        <f>IF('2'!F10&lt;&gt;"",'2'!F10,"")</f>
-        <v/>
-      </c>
-      <c r="I12" s="4" t="str">
-        <f>IF('2'!G10&lt;&gt;"",'2'!G10,"")</f>
+        <f>IF(Data!A10&gt;0,Data!A10,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="1" t="str">
+        <f>IF(Data!B10&lt;&gt;"",Data!B10,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f>IF(Data!C10&lt;&gt;"",Data!C10,"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="1" t="str">
+        <f>IF(Data!D10&lt;&gt;"",Data!D10,"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="1" t="str">
+        <f>IF(Data!E10&lt;&gt;"",Data!E10,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="1" t="str">
+        <f>IF(Data!F10&lt;&gt;"",Data!F10,"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="1" t="str">
+        <f>IF(Data!G10&lt;&gt;"",Data!G10,"")</f>
         <v/>
       </c>
     </row>
@@ -751,31 +750,31 @@
         <v>10</v>
       </c>
       <c r="C13" s="2" t="str">
-        <f>IF('2'!A11&gt;0,'2'!A11,"")</f>
-        <v/>
-      </c>
-      <c r="D13" s="4" t="str">
-        <f>IF('2'!B11&lt;&gt;"",'2'!B11,"")</f>
-        <v/>
-      </c>
-      <c r="E13" s="4" t="str">
-        <f>IF('2'!C11&lt;&gt;"",'2'!C11,"")</f>
-        <v/>
-      </c>
-      <c r="F13" s="4" t="str">
-        <f>IF('2'!D11&lt;&gt;"",'2'!D11,"")</f>
-        <v/>
-      </c>
-      <c r="G13" s="4" t="str">
-        <f>IF('2'!E11&lt;&gt;"",'2'!E11,"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="4" t="str">
-        <f>IF('2'!F11&lt;&gt;"",'2'!F11,"")</f>
-        <v/>
-      </c>
-      <c r="I13" s="4" t="str">
-        <f>IF('2'!G11&lt;&gt;"",'2'!G11,"")</f>
+        <f>IF(Data!A11&gt;0,Data!A11,"")</f>
+        <v/>
+      </c>
+      <c r="D13" s="1" t="str">
+        <f>IF(Data!B11&lt;&gt;"",Data!B11,"")</f>
+        <v/>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f>IF(Data!C11&lt;&gt;"",Data!C11,"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="1" t="str">
+        <f>IF(Data!D11&lt;&gt;"",Data!D11,"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="1" t="str">
+        <f>IF(Data!E11&lt;&gt;"",Data!E11,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="1" t="str">
+        <f>IF(Data!F11&lt;&gt;"",Data!F11,"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="1" t="str">
+        <f>IF(Data!G11&lt;&gt;"",Data!G11,"")</f>
         <v/>
       </c>
     </row>
